--- a/artfynd/A 18428-2026 artfynd.xlsx
+++ b/artfynd/A 18428-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132661308</v>
       </c>
       <c r="B2" t="n">
-        <v>57137</v>
+        <v>57141</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>132661289</v>
       </c>
       <c r="B3" t="n">
-        <v>57137</v>
+        <v>57141</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>132661367</v>
       </c>
       <c r="B4" t="n">
-        <v>57137</v>
+        <v>57141</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         <v>132660660</v>
       </c>
       <c r="B5" t="n">
-        <v>57137</v>
+        <v>57141</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
         <v>132661429</v>
       </c>
       <c r="B6" t="n">
-        <v>57137</v>
+        <v>57141</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
         <v>132660037</v>
       </c>
       <c r="B7" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>132660450</v>
       </c>
       <c r="B8" t="n">
-        <v>57137</v>
+        <v>57141</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 18428-2026 artfynd.xlsx
+++ b/artfynd/A 18428-2026 artfynd.xlsx
@@ -1053,7 +1053,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132660660</v>
+        <v>132661429</v>
       </c>
       <c r="B5" t="n">
         <v>57141</v>
@@ -1107,10 +1107,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>478797</v>
+        <v>478957</v>
       </c>
       <c r="R5" t="n">
-        <v>6572337</v>
+        <v>6572262</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1179,7 +1179,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132661429</v>
+        <v>132660660</v>
       </c>
       <c r="B6" t="n">
         <v>57141</v>
@@ -1233,10 +1233,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>478957</v>
+        <v>478797</v>
       </c>
       <c r="R6" t="n">
-        <v>6572262</v>
+        <v>6572337</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1268,7 +1268,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 18428-2026 artfynd.xlsx
+++ b/artfynd/A 18428-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132661308</v>
       </c>
       <c r="B2" t="n">
-        <v>57141</v>
+        <v>57142</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>132661289</v>
       </c>
       <c r="B3" t="n">
-        <v>57141</v>
+        <v>57142</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>132661367</v>
       </c>
       <c r="B4" t="n">
-        <v>57141</v>
+        <v>57142</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         <v>132661429</v>
       </c>
       <c r="B5" t="n">
-        <v>57141</v>
+        <v>57142</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
         <v>132660660</v>
       </c>
       <c r="B6" t="n">
-        <v>57141</v>
+        <v>57142</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
         <v>132660037</v>
       </c>
       <c r="B7" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>132660450</v>
       </c>
       <c r="B8" t="n">
-        <v>57141</v>
+        <v>57142</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 18428-2026 artfynd.xlsx
+++ b/artfynd/A 18428-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,64 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132661308</v>
+        <v>132659858</v>
       </c>
       <c r="B2" t="n">
-        <v>57145</v>
+        <v>79373</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Näsmossen, Näsmossen, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>478909</v>
+        <v>478658</v>
       </c>
       <c r="R2" t="n">
-        <v>6572293</v>
+        <v>6572287</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -764,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -801,64 +782,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132661289</v>
+        <v>132660037</v>
       </c>
       <c r="B3" t="n">
-        <v>57145</v>
+        <v>79373</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Näsmossen, Näsmossen, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>478908</v>
+        <v>478675</v>
       </c>
       <c r="R3" t="n">
-        <v>6572293</v>
+        <v>6572309</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -890,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -900,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -927,64 +889,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132661367</v>
+        <v>132658722</v>
       </c>
       <c r="B4" t="n">
-        <v>57145</v>
+        <v>79459</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>6450</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
+          <t>(Ach.) Parrique</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Näsmossen, Näsmossen, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>478936</v>
+        <v>478672</v>
       </c>
       <c r="R4" t="n">
-        <v>6572281</v>
+        <v>6572273</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1016,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1026,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1053,64 +996,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132661429</v>
+        <v>132659774</v>
       </c>
       <c r="B5" t="n">
-        <v>57145</v>
+        <v>79459</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>6450</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
+          <t>(Ach.) Parrique</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Näsmossen, Näsmossen, Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>478957</v>
+        <v>478677</v>
       </c>
       <c r="R5" t="n">
-        <v>6572262</v>
+        <v>6572276</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1142,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1152,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1179,64 +1103,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132660660</v>
+        <v>132659805</v>
       </c>
       <c r="B6" t="n">
-        <v>57145</v>
+        <v>79459</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>6450</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
+          <t>(Ach.) Parrique</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Näsmossen, Näsmossen, Vrm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>478797</v>
+        <v>478662</v>
       </c>
       <c r="R6" t="n">
-        <v>6572337</v>
+        <v>6572292</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1268,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1278,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1305,45 +1210,65 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132660037</v>
+        <v>132660450</v>
       </c>
       <c r="B7" t="n">
-        <v>79333</v>
+        <v>57162</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Näsmossen, Näsmossen, Vrm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>478675</v>
+        <v>478831</v>
       </c>
       <c r="R7" t="n">
-        <v>6572309</v>
+        <v>6572323</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1375,7 +1300,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1385,7 +1310,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1412,10 +1337,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132660450</v>
+        <v>132660660</v>
       </c>
       <c r="B8" t="n">
-        <v>57145</v>
+        <v>57162</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1460,17 +1385,16 @@
           <t>äldre spillning</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Näsmossen, Näsmossen, Vrm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>478831</v>
+        <v>478797</v>
       </c>
       <c r="R8" t="n">
-        <v>6572323</v>
+        <v>6572337</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1502,7 +1426,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1512,7 +1436,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1536,6 +1460,1266 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>132660777</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Näsmossen, Näsmossen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>478831</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6572305</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>132660836</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Näsmossen, Näsmossen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>478837</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6572280</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>132660904</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Näsmossen, Näsmossen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>478833</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6572269</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>132661140</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Näsmossen, Näsmossen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>478836</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6572269</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>132661159</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Näsmossen, Näsmossen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>478817</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6572247</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>132661289</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Näsmossen, Näsmossen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>478908</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6572293</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>132661308</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Näsmossen, Näsmossen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>478909</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6572293</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>132661367</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Näsmossen, Näsmossen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>478936</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6572281</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>132661429</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Näsmossen, Näsmossen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>478957</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6572262</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>132661735</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Näsmossen, Näsmossen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>478942</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6572222</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 18428-2026 artfynd.xlsx
+++ b/artfynd/A 18428-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AZ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132659858</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132660037</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132658722</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132659774</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132659805</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1334,6 +1364,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132660450</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1460,6 +1495,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132660660</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1586,6 +1626,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132660777</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1712,6 +1757,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132660836</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1838,6 +1888,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132660904</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1964,6 +2019,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132661140</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2090,6 +2150,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132661159</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2216,6 +2281,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132661289</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2342,6 +2412,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132661308</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2468,6 +2543,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132661367</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2594,6 +2674,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132661429</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2720,8 +2805,32 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132661735</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>